--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>저주</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>각성</t>
         </is>
       </c>
     </row>
@@ -590,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -750,6 +762,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>Curse</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Awakening</t>
         </is>
       </c>
     </row>
@@ -764,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -924,6 +948,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>呪い</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>覚醒</t>
         </is>
       </c>
     </row>
@@ -938,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1101,6 +1137,18 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>觉醒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -588,6 +588,54 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>item.potion.blue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>파란 물약</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>item.potion.electric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>전격 물약</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>item.potion.fire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>화염 물약</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>item.potion.ice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>냉기 물약</t>
         </is>
       </c>
     </row>
@@ -602,7 +650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -774,6 +822,54 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>Awakening</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>item.potion.blue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Blue Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>item.potion.electric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Electric Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>item.potion.fire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fire Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>item.potion.ice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ice Potion</t>
         </is>
       </c>
     </row>
@@ -788,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -960,6 +1056,54 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>item.potion.blue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>青いポーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>item.potion.electric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>電撃のポーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>item.potion.fire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>火炎のポーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>item.potion.ice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>冷気のポーション</t>
         </is>
       </c>
     </row>
@@ -974,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1293,54 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>item.potion.blue</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蓝色药水</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>item.potion.electric</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>电击药水</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>item.potion.fire</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>火焰药水</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>item.potion.ice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>冰霜药水</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,42 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>냉기 물약</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>가속 각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>연산 각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>과부하 각성</t>
         </is>
       </c>
     </row>
@@ -650,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -870,6 +906,42 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Ice Potion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Accelerated Awakening</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Calculated Awakening</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Overload Awakening</t>
         </is>
       </c>
     </row>
@@ -884,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1104,6 +1176,42 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>冷気のポーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>加速覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>演算覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>過負荷覚醒</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1341,6 +1449,42 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>加速觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>运算觉醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>buff.fighter_awakening_evo3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>过载觉醒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -672,6 +672,30 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>과부하 각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>제압 폭격</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>화력 관제</t>
         </is>
       </c>
     </row>
@@ -686,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -942,6 +966,30 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Overload Awakening</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Suppression Barrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fire Control</t>
         </is>
       </c>
     </row>
@@ -956,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1212,6 +1260,30 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>過負荷覚醒</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>制圧爆撃</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>火力管制</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1557,30 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>压制轰炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>buff.gunner_bombard_evo2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>火力管控</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -672,30 +672,6 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>과부하 각성</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>제압 폭격</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>화력 관제</t>
         </is>
       </c>
     </row>
@@ -710,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -966,30 +942,6 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Overload Awakening</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Suppression Barrage</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fire Control</t>
         </is>
       </c>
     </row>
@@ -1004,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1260,30 +1212,6 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>過負荷覚醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>制圧爆撃</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>火力管制</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1557,30 +1485,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>压制轰炸</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>buff.gunner_bombard_evo2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>火力管控</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
+++ b/Assets/Resources/DataFiles/BuffData/1. ExcelFile/BuffLabel.xlsx
@@ -20,13 +20,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,11 +421,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,6 +440,11 @@
           <t>buffName</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +457,11 @@
           <t>공격 강화</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 공격력이 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -458,6 +474,11 @@
           <t>방어 태세</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 방어력이 크게 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,6 +491,11 @@
           <t>신속</t>
         </is>
       </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>이동 속도와 공격 속도가 함께 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -482,6 +508,11 @@
           <t>마나 순환</t>
         </is>
       </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>마나 재생력이 증가합니다. 중첩 가능.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -494,6 +525,11 @@
           <t>집중</t>
         </is>
       </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>치명타 확률이 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -506,6 +542,11 @@
           <t>가속 지대</t>
         </is>
       </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>지대 안에 있는 동안 이동 속도가 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -518,6 +559,7 @@
           <t>새 버프</t>
         </is>
       </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -530,6 +572,11 @@
           <t>둔화</t>
         </is>
       </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>이동 속도가 감소합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -542,6 +589,11 @@
           <t>약화</t>
         </is>
       </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>공격력이 감소합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -554,6 +606,11 @@
           <t>방어구 파괴</t>
         </is>
       </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>방어력이 감소합니다. 중첩 가능.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -566,6 +623,11 @@
           <t>속박</t>
         </is>
       </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>짧은 시간 이동할 수 없습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -578,6 +640,11 @@
           <t>저주</t>
         </is>
       </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>공격력과 방어력이 함께 감소합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -590,6 +657,11 @@
           <t>각성</t>
         </is>
       </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 전투 능력이 크게 향상됩니다.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -602,6 +674,11 @@
           <t>파란 물약</t>
         </is>
       </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 이동 속도가 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -614,6 +691,11 @@
           <t>전격 물약</t>
         </is>
       </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 전격 피해가 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -626,6 +708,11 @@
           <t>화염 물약</t>
         </is>
       </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 화염 피해가 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -638,6 +725,11 @@
           <t>냉기 물약</t>
         </is>
       </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 냉기 피해가 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -650,6 +742,11 @@
           <t>가속 각성</t>
         </is>
       </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 공격 속도와 일반공격 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -662,6 +759,11 @@
           <t>연산 각성</t>
         </is>
       </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>일정 시간 동안 스킬 재사용 대기시간이 줄고 스킬 피해가 크게 증가합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -672,6 +774,28 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>과부하 각성</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>짧은 시간 동안 능력치가 크게 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>skill.fighter.dash.evo3.damage_boost</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>대시 강타</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>대시 직후 잠시 공격력이 증가합니다.</t>
         </is>
       </c>
     </row>
@@ -686,11 +810,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -704,6 +829,11 @@
           <t>buffName</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -716,6 +846,11 @@
           <t>Attack Up</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Increases Attack for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -728,6 +863,11 @@
           <t>Defensive Stance</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Greatly increases Defense for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -740,6 +880,11 @@
           <t>Haste</t>
         </is>
       </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Increases both Movement Speed and Attack Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -752,6 +897,11 @@
           <t>Mana Flow</t>
         </is>
       </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Increases Mana Regeneration. Stackable.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,6 +914,11 @@
           <t>Focus</t>
         </is>
       </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Increases Critical Rate.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,6 +931,11 @@
           <t>Haste Zone</t>
         </is>
       </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Increases Movement Speed while inside the zone.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,6 +948,7 @@
           <t>New Buff</t>
         </is>
       </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,6 +961,11 @@
           <t>Slow</t>
         </is>
       </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Reduces Movement Speed.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -812,6 +978,11 @@
           <t>Weaken</t>
         </is>
       </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Reduces Attack.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -824,6 +995,11 @@
           <t>Armor Break</t>
         </is>
       </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Reduces Defense. Stackable.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -836,6 +1012,11 @@
           <t>Bind</t>
         </is>
       </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Cannot move for a short time.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -848,6 +1029,11 @@
           <t>Curse</t>
         </is>
       </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Reduces both Attack and Defense.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -860,6 +1046,11 @@
           <t>Awakening</t>
         </is>
       </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Greatly enhances combat ability for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -872,6 +1063,11 @@
           <t>Blue Potion</t>
         </is>
       </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Increases Movement Speed for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -884,6 +1080,11 @@
           <t>Electric Potion</t>
         </is>
       </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Increases Electric damage for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -896,6 +1097,11 @@
           <t>Fire Potion</t>
         </is>
       </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Increases Fire damage for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -908,6 +1114,11 @@
           <t>Ice Potion</t>
         </is>
       </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Increases Ice damage for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -920,6 +1131,11 @@
           <t>Accelerated Awakening</t>
         </is>
       </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Greatly increases Attack Speed and basic attack damage for a duration.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -932,6 +1148,11 @@
           <t>Calculated Awakening</t>
         </is>
       </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>For a duration, reduces skill cooldowns and greatly increases skill damage.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -942,6 +1163,28 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Overload Awakening</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Greatly increases stats for a short time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>skill.fighter.dash.evo3.damage_boost</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Dash Strike</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Briefly increases Attack right after a dash.</t>
         </is>
       </c>
     </row>
@@ -956,11 +1199,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -974,6 +1218,11 @@
           <t>buffName</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -986,6 +1235,11 @@
           <t>攻撃強化</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、攻撃力が上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -998,6 +1252,11 @@
           <t>防御態勢</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、防御力が大きく上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1010,6 +1269,11 @@
           <t>迅速</t>
         </is>
       </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>移動速度と攻撃速度が共に上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1022,6 +1286,11 @@
           <t>マナ循環</t>
         </is>
       </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>マナ回復量が上昇します。重複可能。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1034,6 +1303,11 @@
           <t>集中</t>
         </is>
       </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>クリティカル率が上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1046,6 +1320,11 @@
           <t>加速地帯</t>
         </is>
       </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>地帯内にいる間、移動速度が上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1058,6 +1337,7 @@
           <t>新規バフ</t>
         </is>
       </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1070,6 +1350,11 @@
           <t>鈍化</t>
         </is>
       </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>移動速度が低下します。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1082,6 +1367,11 @@
           <t>弱体化</t>
         </is>
       </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>攻撃力が低下します。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1094,6 +1384,11 @@
           <t>防具破壊</t>
         </is>
       </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>防御力が低下します。重複可能。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1106,6 +1401,11 @@
           <t>束縛</t>
         </is>
       </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>短時間、移動できなくなります。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1118,6 +1418,11 @@
           <t>呪い</t>
         </is>
       </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>攻撃力と防御力が共に低下します。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1130,6 +1435,11 @@
           <t>覚醒</t>
         </is>
       </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、戦闘能力が大きく向上します。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1142,6 +1452,11 @@
           <t>青いポーション</t>
         </is>
       </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、移動速度が上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1154,6 +1469,11 @@
           <t>電撃のポーション</t>
         </is>
       </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、電撃ダメージが上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1166,6 +1486,11 @@
           <t>火炎のポーション</t>
         </is>
       </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、火炎ダメージが上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1178,6 +1503,11 @@
           <t>冷気のポーション</t>
         </is>
       </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、冷気ダメージが上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1190,6 +1520,11 @@
           <t>加速覚醒</t>
         </is>
       </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、攻撃速度と通常攻撃ダメージが大きく上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1202,6 +1537,11 @@
           <t>演算覚醒</t>
         </is>
       </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>一定時間、スキルの再使用待機時間が短縮され、スキルダメージが大きく上昇します。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1212,6 +1552,28 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>過負荷覚醒</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>短時間、能力値が大きく上昇します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>skill.fighter.dash.evo3.damage_boost</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>ダッシュ強打</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>ダッシュ直後、しばらく攻撃力が上昇します。</t>
         </is>
       </c>
     </row>
@@ -1226,11 +1588,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1244,6 +1607,11 @@
           <t>buffName</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1256,6 +1624,11 @@
           <t>攻击强化</t>
         </is>
       </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内提高攻击力。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1268,6 +1641,11 @@
           <t>防御姿态</t>
         </is>
       </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内大幅提高防御力。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1280,6 +1658,11 @@
           <t>迅捷</t>
         </is>
       </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>同时提高移动速度和攻击速度。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1292,6 +1675,11 @@
           <t>法力循环</t>
         </is>
       </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>提高法力恢复。可叠加。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1304,6 +1692,11 @@
           <t>专注</t>
         </is>
       </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>提高暴击率。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1316,6 +1709,11 @@
           <t>加速地带</t>
         </is>
       </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>处于地带内时提高移动速度。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1328,6 +1726,7 @@
           <t>新增增益</t>
         </is>
       </c>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1340,6 +1739,11 @@
           <t>迟缓</t>
         </is>
       </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>降低移动速度。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1352,6 +1756,11 @@
           <t>弱化</t>
         </is>
       </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>降低攻击力。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1364,6 +1773,11 @@
           <t>破甲</t>
         </is>
       </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>降低防御力。可叠加。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1376,6 +1790,11 @@
           <t>束缚</t>
         </is>
       </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>短时间内无法移动。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1388,6 +1807,11 @@
           <t>诅咒</t>
         </is>
       </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>同时降低攻击力和防御力。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1400,6 +1824,11 @@
           <t>觉醒</t>
         </is>
       </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内大幅提升战斗能力。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1412,6 +1841,11 @@
           <t>蓝色药水</t>
         </is>
       </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内提高移动速度。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1424,6 +1858,11 @@
           <t>电击药水</t>
         </is>
       </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内提高电击伤害。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1436,6 +1875,11 @@
           <t>火焰药水</t>
         </is>
       </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内提高火焰伤害。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1448,6 +1892,11 @@
           <t>冰霜药水</t>
         </is>
       </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内提高冰霜伤害。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1460,6 +1909,11 @@
           <t>加速觉醒</t>
         </is>
       </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内大幅提高攻击速度和普通攻击伤害。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,6 +1926,11 @@
           <t>运算觉醒</t>
         </is>
       </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>一定时间内缩短技能冷却时间，并大幅提高技能伤害。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1482,6 +1941,28 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>过载觉醒</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>短时间内大幅提高各项能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>skill.fighter.dash.evo3.damage_boost</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>冲刺强击</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>冲刺后短时间内提高攻击力。</t>
         </is>
       </c>
     </row>
